--- a/05_App/benchmark/healthcare_benchmark.xlsx
+++ b/05_App/benchmark/healthcare_benchmark.xlsx
@@ -743,7 +743,11 @@
           <t>CEA Minimum Standards, Record-keeping requirements</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -770,7 +774,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 42</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -797,7 +805,11 @@
           <t>Ayushman Bharat PM-JAY operational guidelines</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -824,7 +836,11 @@
           <t>National Medical Commission Act, 2019, Section 31</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -851,7 +867,11 @@
           <t>CEA Minimum Standards - Clinic/Polyclinic category</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -878,7 +898,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 3</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -905,7 +929,11 @@
           <t>CEA Minimum Standards for Hospitals (Level 2)</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -932,7 +960,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 11</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -959,7 +991,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 16</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -986,7 +1022,11 @@
           <t>Atomic Energy (Radiation Protection) Rules, 2004</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://aerb.gov.in/english/images/aerb/LegalDocuments/Radiation_Protection_Rules_2004.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -1013,7 +1053,11 @@
           <t>NMC Compulsory Rotating Medical Internship Regulations, 2021</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/information-desk/for-students-doctors/regulations/</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -1040,7 +1084,11 @@
           <t>CEA Minimum Standards for Hospitals (Level 3)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -1067,7 +1115,11 @@
           <t>PM-JAY Operational Guidelines, Empanelment and Claims chapter</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -1094,7 +1146,11 @@
           <t>CEA Minimum Standards, Display requirements</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -1121,7 +1177,11 @@
           <t>National Medical Commission Act, 2019, Section 5</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -1148,7 +1208,11 @@
           <t>CEA Minimum Standards, Space requirements</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -1175,7 +1239,11 @@
           <t>Bio-Medical Waste Management Rules, 2016, Schedule I</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -1202,7 +1270,11 @@
           <t>National Medical Commission Act, 2019, Sections 20-22</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -1229,7 +1301,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 23 and 42</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
@@ -1256,7 +1332,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 16 and 17</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -1283,7 +1363,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 18</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Candidates may incorrectly think deemed registration means permanent exemption from standards.</t>
@@ -1314,7 +1398,11 @@
           <t>PM-JAY Operational Guidelines</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -1341,7 +1429,11 @@
           <t>National Medical Commission Act, 2019, Section 49(4); related NMC notifications</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Bridge courses are controversial; candidates may conflate them with full MBBS equivalence.</t>
@@ -1372,7 +1464,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 2; Constitution of India</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
@@ -1399,7 +1495,11 @@
           <t>General principles of statutory interpretation; CEA corpus structure</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -1426,7 +1526,11 @@
           <t>Bio-Medical Waste Management Rules, 2016 vs. BMW Management and Handling Rules, 1998</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Candidates may reference a non-existent 2011 revision.</t>
@@ -1457,7 +1561,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 2(c); Pharmacy Act 1948</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -1484,7 +1592,11 @@
           <t>National Medical Commission Act, 2019, Sections 25-30</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -1511,7 +1623,11 @@
           <t>CEA Minimum Standards; Department of Health &amp; Family Welfare guidelines on Citizen's Charter</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
@@ -1538,7 +1654,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations, 2002, Regulation 1.3</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Candidates may think emergency treatment without consent is always legally protected without qualification.</t>
@@ -1569,7 +1689,11 @@
           <t>PM-JAY Operational Guidelines, Portability chapter</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34" ht="60" customHeight="1">
@@ -1596,7 +1720,11 @@
           <t>Epidemic Diseases Act, 1897; State-specific epidemic disease regulations</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/2155/1/192104.pdf</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
@@ -1623,7 +1751,11 @@
           <t>CEA Act, 2010; NABH Standards</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Many candidates conflate NABH accreditation with CEA registration as equivalent requirements.</t>
@@ -1654,7 +1786,11 @@
           <t>National Medical Commission Act, 2019, Section 32</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="60" customHeight="1">
@@ -1681,7 +1817,11 @@
           <t>PM-JAY Operational Guidelines, De-empanelment provisions</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38" ht="60" customHeight="1">
@@ -1708,7 +1848,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 10 and 12</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="60" customHeight="1">
@@ -1735,7 +1879,11 @@
           <t>Drugs and Cosmetics Act, 1940; CDSCO Blood Bank Guidelines</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2022/acts_and_rules/Drugs%20and%20Cosmetics%20Act,%201940.pdf</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="60" customHeight="1">
@@ -1762,7 +1910,11 @@
           <t>CEA Minimum Standards; Supreme Court of India judgments on emergency medical treatment</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Private hospitals often impose deposits before emergency care, which violates this standard.</t>
@@ -1793,7 +1945,11 @@
           <t>Telemedicine Practice Guidelines, 2020 (MCI/NMC); IMC Act 1956</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/pdf/Telemedicine.pdf</t>
+        </is>
+      </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Prescribing controlled substances on first telemedicine contact is not allowed.</t>
@@ -1824,7 +1980,11 @@
           <t>CEA 2010, Sections 16, 17, 19; CEA Minimum Standards</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G42" s="6" t="inlineStr"/>
     </row>
     <row r="43" ht="60" customHeight="1">
@@ -1851,7 +2011,11 @@
           <t>PM-JAY Operational Guidelines, Referral and Claims</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Hospitals often try to bill diagnostic services at third-party labs under PM-JAY, which is not permitted.</t>
@@ -1882,7 +2046,11 @@
           <t>National Medical Commission Act, 2019, Section 32; NMC transition notifications</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
@@ -1909,7 +2077,11 @@
           <t>Bio-Medical Waste Management Rules, 2016, Rule 4</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="60" customHeight="1">
@@ -1936,7 +2108,11 @@
           <t>IMC (Professional Conduct) Regulations 2002; Consumer Protection Act 2019; CPC provisions</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Hospitals cannot deny records to the legal next of kin of a deceased patient.</t>
@@ -1967,7 +2143,11 @@
           <t>CEA Minimum Standards; Section 12 CEA 2010</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Single-doctor exemption from registration (in some States) is sometimes conflated with exemption from standards.</t>
@@ -1998,7 +2178,11 @@
           <t>CEA Minimum Standards, Infection Control requirements</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G48" s="6" t="inlineStr"/>
     </row>
     <row r="49" ht="60" customHeight="1">
@@ -2025,7 +2209,11 @@
           <t>Atomic Energy (Radiation Protection) Rules 2004; PCPNDT Act 1994</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>https://aerb.gov.in/english/images/aerb/LegalDocuments/Radiation_Protection_Rules_2004.pdf</t>
+        </is>
+      </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Many assume all ultrasound requires AERB licence; it only applies to ionizing radiation equipment.</t>
@@ -2056,7 +2244,11 @@
           <t>PM-JAY Operational Guidelines, Fraud and Abuse Management chapter</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="60" customHeight="1">
@@ -2083,7 +2275,11 @@
           <t>CEA 2010, Section 11; CEA Minimum Standards for Mobile Facilities</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
@@ -2110,7 +2306,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 25-27</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G52" s="6" t="inlineStr"/>
     </row>
     <row r="53" ht="60" customHeight="1">
@@ -2137,7 +2337,11 @@
           <t>CEA 2010; Drugs and Cosmetics Act 1940; BMW Rules 2016</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
@@ -2164,7 +2368,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations 2002; CEA Minimum Standards for surgical facilities</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Rural necessity is not a legal defence for performing procedures beyond one's qualification.</t>
@@ -2195,7 +2403,11 @@
           <t>Digital Personal Data Protection Act 2023; IT Act 2000; IMC Ethics Regulations</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="60" customHeight="1">
@@ -2222,7 +2434,11 @@
           <t>CEA 2010; IPC Section 304A; State-specific regulations</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="60" customHeight="1">
@@ -2249,7 +2465,11 @@
           <t>CEA Minimum Standards, Record Retention; Indian Evidence Act</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
           <t>2-year internal policy does not override the statutory minimum retention period.</t>
@@ -2280,7 +2500,11 @@
           <t>PM-JAY Operational Guidelines, Patient Rights and Hospital Obligations</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Hospitals routinely charge top-ups; this is prohibited for scheme-covered services.</t>
@@ -2311,7 +2535,11 @@
           <t>NMC Act 2019, Sections 25-29; NMC Regulations on Establishment of Medical Colleges</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
@@ -2338,7 +2566,11 @@
           <t>Epidemic Diseases Act 1897; State-specific epidemic disease schedules</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/2155/1/192104.pdf</t>
+        </is>
+      </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Lab technicians often assume they must directly report; the primary legal obligation falls on the treating physician.</t>
@@ -2369,7 +2601,11 @@
           <t>CEA 2010, Sections 19 and 20 (transfer provisions)</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -2396,7 +2632,11 @@
           <t>CEA 2010; Drugs and Cosmetics Act 1940; BMW Rules 2016; PM-JAY Operational Guidelines</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63" ht="60" customHeight="1">
@@ -2423,7 +2663,11 @@
           <t>Multiple statutes as identified above</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Sequencing errors are common; AERB licence must precede equipment use, not follow.</t>
@@ -2454,7 +2698,11 @@
           <t>PM-JAY Operational Guidelines; IRDAI guidelines on health insurance; Insurance Act 1938</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
@@ -2481,7 +2729,11 @@
           <t>NMC Act 2019, Sections 31-33; Ethics and Medical Registration Board provisions</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
@@ -2508,7 +2760,11 @@
           <t>Epidemic Diseases Act 1897; Disaster Management Act 2005; CEA 2010</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="inlineStr"/>
     </row>
     <row r="67" ht="60" customHeight="1">
@@ -2535,7 +2791,11 @@
           <t>PM-JAY Operational Guidelines; NABH Standards; CEA 2010</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -2562,7 +2822,11 @@
           <t>NMC Act 2019; Consumer Protection Act 2019; IPC Section 304A; CEA 2010</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
           <t>Many believe criminal and civil/consumer proceedings cannot run simultaneously - they can.</t>
@@ -2593,7 +2857,11 @@
           <t>Medical Devices Rules 2017; Consumer Protection Act 2019; IMC Ethics Regulations; CDSCO guidelines on AI/SaMD</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -2620,7 +2888,11 @@
           <t>Income Tax Act 1961, Section 12A/12AA; CEA 2010; CBDT circulars on charitable hospitals</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71" ht="60" customHeight="1">
@@ -2647,7 +2919,11 @@
           <t>NMC Act 2019; CEA Minimum Standards; State government circulars; Factories Act 1948 (for comparison)</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
@@ -2674,7 +2950,11 @@
           <t>CEA 2010 Section 24; Industrial Disputes Act 1947; BMW Rules 2016; Drugs and Cosmetics Act 1940</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
           <t>Hospitals often destroy records on closure; this violates mandatory retention requirements.</t>
@@ -2705,7 +2985,11 @@
           <t>New Drugs and Clinical Trials Rules, 2019; Drugs and Cosmetics Act 1940; CDSCO Good Clinical Practice Guidelines</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2022/acts_and_rules/Drugs%20and%20Cosmetics%20Act,%201940.pdf</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="60" customHeight="1">
@@ -2732,7 +3016,11 @@
           <t>Pre-Conception and Pre-Natal Diagnostic Techniques (Prohibition of Sex Selection) Act 1994</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>https://mohfw.gov.in/sites/default/files/5954796031.pdf</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
           <t>Many believe inadvertent documentation is excused; the PCPNDT Act is strict liability.</t>
@@ -2763,7 +3051,11 @@
           <t>CEA Minimum Standards; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -2790,7 +3082,11 @@
           <t>CEA 2010 Section 1(3) - State adoption; individual State nursing home acts; national regulations listed above</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -2817,7 +3113,11 @@
           <t>DPDPA 2023; Medical Devices Rules 2017; Consumer Protection Act 2019; NMC Ethics Regulations</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/writereaddata/files/Digital%20Personal%20Data%20Protection%20Act%202023.pdf</t>
+        </is>
+      </c>
       <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="60" customHeight="1">
@@ -2844,7 +3144,11 @@
           <t>PM-JAY Operational Guidelines; NMC Act 2019; IPC; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79" ht="60" customHeight="1">
@@ -2871,7 +3175,11 @@
           <t>CEA 2010, Section 12; Constitution of India, Entry 6 List II; judicial precedents on State health regulation</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -2898,7 +3206,11 @@
           <t>CEA 2010, Section 2 (definition of clinical establishment); District Registration Authority guidelines</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -2925,7 +3237,11 @@
           <t>CrPC Section 357C; IPC Sections 326A-326B; CEA 2010; Supreme Court directions on acid attack treatment</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
           <t>Hospitals sometimes refuse treatment pending police arrival; this is illegal.</t>
@@ -2956,7 +3272,11 @@
           <t>CEA 2010, Section 11; no JCI exemption provision exists in Indian law</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
           <t>JCI accreditation is often (incorrectly) presented as superseding local regulatory requirements.</t>
@@ -2987,7 +3307,11 @@
           <t>NMC Act 2019, Section 59 (savings and transitional provisions)</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
           <t>This is a common trap - abolition of MCI ≠ invalidation of existing registrations.</t>
@@ -3018,7 +3342,11 @@
           <t>PM-JAY Operational Guidelines, Beneficiary Identification chapter; SECC 2011</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
           <t>'Only BPL families' is a common misconception; SECC is the actual basis.</t>
@@ -3049,7 +3377,11 @@
           <t>Consumer Protection Act 2019; IMA v. V.P. Shantha (1995) 6 SCC 651</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
           <t>'Free government hospital = no consumer protection' is a partial truth presented as absolute.</t>
@@ -3080,7 +3412,11 @@
           <t>CEA 2010, Section 2(m) (definition of 'person in charge'); general principles of corporate liability</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Management company vs. owner distinction is a trap used to escape compliance responsibility.</t>
@@ -3111,7 +3447,11 @@
           <t>Drugs and Magic Remedies (Objectionable Advertisements) Act 1954; Consumer Protection Act 2019; AYUSH Ministry guidelines</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Many assume AYUSH practitioners have more advertising freedom; they are equally bound by this Act.</t>
@@ -3142,7 +3482,11 @@
           <t>CEA 2010; General Clauses Act 1897; Supreme Court on delayed rule-making</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
           <t>'No Rules = no compliance' is a trap argument that courts regularly reject.</t>
@@ -3173,7 +3517,11 @@
           <t>CEA 2010; Kerala Private Medical Institutions Act 2015; Constitutional Entries 6 (List II) and 26 (List III)</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Central Act supremacy is often incorrectly used to dismiss State health legislation.</t>
@@ -3204,7 +3552,11 @@
           <t>CEA 2010; Telemedicine Practice Guidelines 2020; NMC Act 2019</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Tech startup framing is used to evade healthcare regulation; courts and regulators look at the substance of services.</t>
@@ -3235,7 +3587,11 @@
           <t>NMC Act 2019; IMC Ethics Regulations; Consumer Protection Act 2019; IPC 304A</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Independent consultant = no personal liability is a classic false belief in healthcare.</t>
@@ -3266,7 +3622,11 @@
           <t>Consumer Protection Act 2019; IMA v. V.P. Shantha 1995 SCC 651</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G92" s="8" t="inlineStr"/>
     </row>
     <row r="93" ht="60" customHeight="1">
@@ -3293,7 +3653,11 @@
           <t>Drugs and Cosmetics Act 1940; Indian Nursing Council Act 1947; NMC Act 2019</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Foreign nurse practitioner prescription rights do not transfer to India.</t>
@@ -3324,7 +3688,11 @@
           <t>PM-JAY Operational Guidelines, Hospital Obligations chapter</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Private hospitals often selectively apply government-scheme display requirements.</t>
@@ -3355,7 +3723,11 @@
           <t>CEA 2010, Section 1(2); Constitution of India, Article 239</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
           <t>A trap that uses a correct premise to reach a false conclusion.</t>
@@ -3386,7 +3758,11 @@
           <t>UCPMP 2024 (Dept. of Pharmaceuticals); IMC/NMC Ethics Regulations 2002, Regulation 6.8</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>https://pharma-dept.gov.in/sites/default/files/UCPMP%202024%20for%20website.pdf</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
           <t>This is a standard pharmaceutical marketing trap; 'company pays, not hospital' does not legalise the arrangement.</t>
@@ -3417,7 +3793,11 @@
           <t>CEA 2010, Section 2(c)(iii)</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
           <t>'We don't treat patients' is one of the most common false defences against CEA registration.</t>
@@ -3448,7 +3828,11 @@
           <t>Bombay Public Trusts Act 1950; Maharashtra healthcare establishment regulations</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>https://nashik.dcourt.gov.in/articles/BPT_ACT_1950.pdf</t>
+        </is>
+      </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Charitable trust registration ≠ healthcare licensing exemption.</t>
@@ -3479,7 +3863,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations 2002, Regulation 1.3.1</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
           <t>'Verbal is legally valid' is technically partially true but professionally and practically unsound for surgery.</t>
@@ -3510,7 +3898,11 @@
           <t>CEA 2010; Goods and Services Tax Act 2017</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
           <t>This is a novel trap argument using unrelated regulatory compliance to claim exemption from a healthcare obligation.</t>
@@ -3541,7 +3933,11 @@
           <t>NMC Act 2019, Section 59 (savings clause); general principles of statutory succession</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
           <t>MCI abolition = void precedents is a classic statutory interpretation error.</t>
@@ -3664,7 +4060,11 @@
           <t>CEA Minimum Standards, Record-keeping requirements</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -3691,7 +4091,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 42</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3718,7 +4122,11 @@
           <t>Ayushman Bharat PM-JAY operational guidelines</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -3745,7 +4153,11 @@
           <t>National Medical Commission Act, 2019, Section 31</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -3772,7 +4184,11 @@
           <t>CEA Minimum Standards - Clinic/Polyclinic category</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -3799,7 +4215,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 3</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -3826,7 +4246,11 @@
           <t>CEA Minimum Standards for Hospitals (Level 2)</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -3853,7 +4277,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 11</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -3880,7 +4308,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 16</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -3907,7 +4339,11 @@
           <t>Atomic Energy (Radiation Protection) Rules, 2004</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://aerb.gov.in/english/images/aerb/LegalDocuments/Radiation_Protection_Rules_2004.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -3934,7 +4370,11 @@
           <t>NMC Compulsory Rotating Medical Internship Regulations, 2021</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/information-desk/for-students-doctors/regulations/</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -3961,7 +4401,11 @@
           <t>CEA Minimum Standards for Hospitals (Level 3)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -3988,7 +4432,11 @@
           <t>PM-JAY Operational Guidelines, Empanelment and Claims chapter</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -4015,7 +4463,11 @@
           <t>CEA Minimum Standards, Display requirements</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -4042,7 +4494,11 @@
           <t>National Medical Commission Act, 2019, Section 5</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -4069,7 +4525,11 @@
           <t>CEA Minimum Standards, Space requirements</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -4096,7 +4556,11 @@
           <t>Bio-Medical Waste Management Rules, 2016, Schedule I</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -4123,7 +4587,11 @@
           <t>National Medical Commission Act, 2019, Sections 20-22</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -4150,7 +4618,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 23 and 42</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4238,7 +4710,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 16 and 17</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -4265,7 +4741,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 18</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Candidates may incorrectly think deemed registration means permanent exemption from standards.</t>
@@ -4296,7 +4776,11 @@
           <t>PM-JAY Operational Guidelines</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -4323,7 +4807,11 @@
           <t>National Medical Commission Act, 2019, Section 49(4); related NMC notifications</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Bridge courses are controversial; candidates may conflate them with full MBBS equivalence.</t>
@@ -4354,7 +4842,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 2; Constitution of India</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -4381,7 +4873,11 @@
           <t>General principles of statutory interpretation; CEA corpus structure</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -4408,7 +4904,11 @@
           <t>Bio-Medical Waste Management Rules, 2016 vs. BMW Management and Handling Rules, 1998</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Candidates may reference a non-existent 2011 revision.</t>
@@ -4439,7 +4939,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Section 2(c); Pharmacy Act 1948</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -4466,7 +4970,11 @@
           <t>National Medical Commission Act, 2019, Sections 25-30</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -4493,7 +5001,11 @@
           <t>CEA Minimum Standards; Department of Health &amp; Family Welfare guidelines on Citizen's Charter</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -4520,7 +5032,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations, 2002, Regulation 1.3</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Candidates may think emergency treatment without consent is always legally protected without qualification.</t>
@@ -4551,7 +5067,11 @@
           <t>PM-JAY Operational Guidelines, Portability chapter</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -4578,7 +5098,11 @@
           <t>Epidemic Diseases Act, 1897; State-specific epidemic disease regulations</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/2155/1/192104.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -4605,7 +5129,11 @@
           <t>CEA Act, 2010; NABH Standards</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Many candidates conflate NABH accreditation with CEA registration as equivalent requirements.</t>
@@ -4636,7 +5164,11 @@
           <t>National Medical Commission Act, 2019, Section 32</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -4663,7 +5195,11 @@
           <t>PM-JAY Operational Guidelines, De-empanelment provisions</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -4690,7 +5226,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 10 and 12</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -4717,7 +5257,11 @@
           <t>Drugs and Cosmetics Act, 1940; CDSCO Blood Bank Guidelines</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2022/acts_and_rules/Drugs%20and%20Cosmetics%20Act,%201940.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -4744,7 +5288,11 @@
           <t>CEA Minimum Standards; Supreme Court of India judgments on emergency medical treatment</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Private hospitals often impose deposits before emergency care, which violates this standard.</t>
@@ -4775,7 +5323,11 @@
           <t>Telemedicine Practice Guidelines, 2020 (MCI/NMC); IMC Act 1956</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/pdf/Telemedicine.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Prescribing controlled substances on first telemedicine contact is not allowed.</t>
@@ -4867,7 +5419,11 @@
           <t>CEA 2010, Sections 16, 17, 19; CEA Minimum Standards</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G2" s="6" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -4894,7 +5450,11 @@
           <t>PM-JAY Operational Guidelines, Referral and Claims</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Hospitals often try to bill diagnostic services at third-party labs under PM-JAY, which is not permitted.</t>
@@ -4925,7 +5485,11 @@
           <t>National Medical Commission Act, 2019, Section 32; NMC transition notifications</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -4952,7 +5516,11 @@
           <t>Bio-Medical Waste Management Rules, 2016, Rule 4</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.egazette.gov.in/WriteReadData/2016/168389.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -4979,7 +5547,11 @@
           <t>IMC (Professional Conduct) Regulations 2002; Consumer Protection Act 2019; CPC provisions</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Hospitals cannot deny records to the legal next of kin of a deceased patient.</t>
@@ -5010,7 +5582,11 @@
           <t>CEA Minimum Standards; Section 12 CEA 2010</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Single-doctor exemption from registration (in some States) is sometimes conflated with exemption from standards.</t>
@@ -5041,7 +5617,11 @@
           <t>CEA Minimum Standards, Infection Control requirements</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -5068,7 +5648,11 @@
           <t>Atomic Energy (Radiation Protection) Rules 2004; PCPNDT Act 1994</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>https://aerb.gov.in/english/images/aerb/LegalDocuments/Radiation_Protection_Rules_2004.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Many assume all ultrasound requires AERB licence; it only applies to ionizing radiation equipment.</t>
@@ -5099,7 +5683,11 @@
           <t>PM-JAY Operational Guidelines, Fraud and Abuse Management chapter</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -5126,7 +5714,11 @@
           <t>CEA 2010, Section 11; CEA Minimum Standards for Mobile Facilities</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -5153,7 +5745,11 @@
           <t>Clinical Establishments (Registration and Regulation) Act, 2010, Sections 25-27</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -5180,7 +5776,11 @@
           <t>CEA 2010; Drugs and Cosmetics Act 1940; BMW Rules 2016</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -5207,7 +5807,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations 2002; CEA Minimum Standards for surgical facilities</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Rural necessity is not a legal defence for performing procedures beyond one's qualification.</t>
@@ -5238,7 +5842,11 @@
           <t>Digital Personal Data Protection Act 2023; IT Act 2000; IMC Ethics Regulations</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -5265,7 +5873,11 @@
           <t>CEA 2010; IPC Section 304A; State-specific regulations</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -5292,7 +5904,11 @@
           <t>CEA Minimum Standards, Record Retention; Indian Evidence Act</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>2-year internal policy does not override the statutory minimum retention period.</t>
@@ -5323,7 +5939,11 @@
           <t>PM-JAY Operational Guidelines, Patient Rights and Hospital Obligations</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Hospitals routinely charge top-ups; this is prohibited for scheme-covered services.</t>
@@ -5354,7 +5974,11 @@
           <t>NMC Act 2019, Sections 25-29; NMC Regulations on Establishment of Medical Colleges</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -5381,7 +6005,11 @@
           <t>Epidemic Diseases Act 1897; State-specific epidemic disease schedules</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/2155/1/192104.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Lab technicians often assume they must directly report; the primary legal obligation falls on the treating physician.</t>
@@ -5412,7 +6040,11 @@
           <t>CEA 2010, Sections 19 and 20 (transfer provisions)</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5500,7 +6132,11 @@
           <t>CEA 2010; Drugs and Cosmetics Act 1940; BMW Rules 2016; PM-JAY Operational Guidelines</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -5527,7 +6163,11 @@
           <t>Multiple statutes as identified above</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Sequencing errors are common; AERB licence must precede equipment use, not follow.</t>
@@ -5558,7 +6198,11 @@
           <t>PM-JAY Operational Guidelines; IRDAI guidelines on health insurance; Insurance Act 1938</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -5585,7 +6229,11 @@
           <t>NMC Act 2019, Sections 31-33; Ethics and Medical Registration Board provisions</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -5612,7 +6260,11 @@
           <t>Epidemic Diseases Act 1897; Disaster Management Act 2005; CEA 2010</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -5639,7 +6291,11 @@
           <t>PM-JAY Operational Guidelines; NABH Standards; CEA 2010</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5666,7 +6322,11 @@
           <t>NMC Act 2019; Consumer Protection Act 2019; IPC Section 304A; CEA 2010</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Many believe criminal and civil/consumer proceedings cannot run simultaneously - they can.</t>
@@ -5697,7 +6357,11 @@
           <t>Medical Devices Rules 2017; Consumer Protection Act 2019; IMC Ethics Regulations; CDSCO guidelines on AI/SaMD</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -5724,7 +6388,11 @@
           <t>Income Tax Act 1961, Section 12A/12AA; CEA 2010; CBDT circulars on charitable hospitals</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -5751,7 +6419,11 @@
           <t>NMC Act 2019; CEA Minimum Standards; State government circulars; Factories Act 1948 (for comparison)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -5778,7 +6450,11 @@
           <t>CEA 2010 Section 24; Industrial Disputes Act 1947; BMW Rules 2016; Drugs and Cosmetics Act 1940</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Hospitals often destroy records on closure; this violates mandatory retention requirements.</t>
@@ -5809,7 +6485,11 @@
           <t>New Drugs and Clinical Trials Rules, 2019; Drugs and Cosmetics Act 1940; CDSCO Good Clinical Practice Guidelines</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2022/acts_and_rules/Drugs%20and%20Cosmetics%20Act,%201940.pdf</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -5836,7 +6516,11 @@
           <t>Pre-Conception and Pre-Natal Diagnostic Techniques (Prohibition of Sex Selection) Act 1994</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>https://mohfw.gov.in/sites/default/files/5954796031.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Many believe inadvertent documentation is excused; the PCPNDT Act is strict liability.</t>
@@ -5867,7 +6551,11 @@
           <t>CEA Minimum Standards; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -5894,7 +6582,11 @@
           <t>CEA 2010 Section 1(3) - State adoption; individual State nursing home acts; national regulations listed above</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -5921,7 +6613,11 @@
           <t>DPDPA 2023; Medical Devices Rules 2017; Consumer Protection Act 2019; NMC Ethics Regulations</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/writereaddata/files/Digital%20Personal%20Data%20Protection%20Act%202023.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -5948,7 +6644,11 @@
           <t>PM-JAY Operational Guidelines; NMC Act 2019; IPC; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -5975,7 +6675,11 @@
           <t>CEA 2010, Section 12; Constitution of India, Entry 6 List II; judicial precedents on State health regulation</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -6002,7 +6706,11 @@
           <t>CEA 2010, Section 2 (definition of clinical establishment); District Registration Authority guidelines</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -6029,7 +6737,11 @@
           <t>CrPC Section 357C; IPC Sections 326A-326B; CEA 2010; Supreme Court directions on acid attack treatment</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Hospitals sometimes refuse treatment pending police arrival; this is illegal.</t>
@@ -6121,7 +6833,11 @@
           <t>CEA 2010, Section 11; no JCI exemption provision exists in Indian law</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>JCI accreditation is often (incorrectly) presented as superseding local regulatory requirements.</t>
@@ -6152,7 +6868,11 @@
           <t>NMC Act 2019, Section 59 (savings and transitional provisions)</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>This is a common trap - abolition of MCI ≠ invalidation of existing registrations.</t>
@@ -6183,7 +6903,11 @@
           <t>PM-JAY Operational Guidelines, Beneficiary Identification chapter; SECC 2011</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>'Only BPL families' is a common misconception; SECC is the actual basis.</t>
@@ -6214,7 +6938,11 @@
           <t>Consumer Protection Act 2019; IMA v. V.P. Shantha (1995) 6 SCC 651</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>'Free government hospital = no consumer protection' is a partial truth presented as absolute.</t>
@@ -6245,7 +6973,11 @@
           <t>CEA 2010, Section 2(m) (definition of 'person in charge'); general principles of corporate liability</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Management company vs. owner distinction is a trap used to escape compliance responsibility.</t>
@@ -6276,7 +7008,11 @@
           <t>Drugs and Magic Remedies (Objectionable Advertisements) Act 1954; Consumer Protection Act 2019; AYUSH Ministry guidelines</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Many assume AYUSH practitioners have more advertising freedom; they are equally bound by this Act.</t>
@@ -6307,7 +7043,11 @@
           <t>CEA 2010; General Clauses Act 1897; Supreme Court on delayed rule-making</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>'No Rules = no compliance' is a trap argument that courts regularly reject.</t>
@@ -6338,7 +7078,11 @@
           <t>CEA 2010; Kerala Private Medical Institutions Act 2015; Constitutional Entries 6 (List II) and 26 (List III)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Central Act supremacy is often incorrectly used to dismiss State health legislation.</t>
@@ -6369,7 +7113,11 @@
           <t>CEA 2010; Telemedicine Practice Guidelines 2020; NMC Act 2019</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Tech startup framing is used to evade healthcare regulation; courts and regulators look at the substance of services.</t>
@@ -6400,7 +7148,11 @@
           <t>NMC Act 2019; IMC Ethics Regulations; Consumer Protection Act 2019; IPC 304A</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Independent consultant = no personal liability is a classic false belief in healthcare.</t>
@@ -6431,7 +7183,11 @@
           <t>Consumer Protection Act 2019; IMA v. V.P. Shantha 1995 SCC 651</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.nic.in/sites/default/files/CP%20Act%2C%202019.pdf</t>
+        </is>
+      </c>
       <c r="G12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -6458,7 +7214,11 @@
           <t>Drugs and Cosmetics Act 1940; Indian Nursing Council Act 1947; NMC Act 2019</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Foreign nurse practitioner prescription rights do not transfer to India.</t>
@@ -6489,7 +7249,11 @@
           <t>PM-JAY Operational Guidelines, Hospital Obligations chapter</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>https://pmjay.gov.in/sites/default/files/2022-08/PM-JAY_Operational_Guidelines_V5.pdf</t>
+        </is>
+      </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Private hospitals often selectively apply government-scheme display requirements.</t>
@@ -6520,7 +7284,11 @@
           <t>CEA 2010, Section 1(2); Constitution of India, Article 239</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>A trap that uses a correct premise to reach a false conclusion.</t>
@@ -6551,7 +7319,11 @@
           <t>UCPMP 2024 (Dept. of Pharmaceuticals); IMC/NMC Ethics Regulations 2002, Regulation 6.8</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>https://pharma-dept.gov.in/sites/default/files/UCPMP%202024%20for%20website.pdf</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>This is a standard pharmaceutical marketing trap; 'company pays, not hospital' does not legalise the arrangement.</t>
@@ -6582,7 +7354,11 @@
           <t>CEA 2010, Section 2(c)(iii)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>'We don't treat patients' is one of the most common false defences against CEA registration.</t>
@@ -6613,7 +7389,11 @@
           <t>Bombay Public Trusts Act 1950; Maharashtra healthcare establishment regulations</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>https://nashik.dcourt.gov.in/articles/BPT_ACT_1950.pdf</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Charitable trust registration ≠ healthcare licensing exemption.</t>
@@ -6644,7 +7424,11 @@
           <t>IMC (Professional Conduct, Etiquette and Ethics) Regulations 2002, Regulation 1.3.1</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/Rules-Regulations/Ethics%20Regulations%202002.pdf</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
           <t>'Verbal is legally valid' is technically partially true but professionally and practically unsound for surgery.</t>
@@ -6675,7 +7459,11 @@
           <t>CEA 2010; Goods and Services Tax Act 2017</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>http://clinicalestablishments.gov.in/WriteReadData/912.pdf</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>This is a novel trap argument using unrelated regulatory compliance to claim exemption from a healthcare obligation.</t>
@@ -6706,7 +7494,11 @@
           <t>NMC Act 2019, Section 59 (savings clause); general principles of statutory succession</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nmc.org.in/MCIRest/open/getDocument?path=/WC/file-manager/PHD/NMC-Act-English.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>MCI abolition = void precedents is a classic statutory interpretation error.</t>
